--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="208">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
@@ -596,16 +599,16 @@
 </t>
   </si>
   <si>
-    <t>localisation anatomique</t>
+    <t>localisation anatomique. Le code de la localisation doit être issu de SNOMED CT (2.16.840.1.113883.6.96)</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.approachSiteCode</t>
+  </si>
+  <si>
+    <t>Voie d’abord</t>
   </si>
   <si>
     <t>SNOMED CT (2.16.840.1.113883.6.96)</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.approachSiteCode</t>
-  </si>
-  <si>
-    <t>Voie d’abord</t>
   </si>
   <si>
     <t>fr-lm-procedure.difficulty</t>
@@ -639,6 +642,9 @@
   </si>
   <si>
     <t>Complication survenue pendant l'acte ou immédiatement après uniquement.</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): ICD-10, SNOMED CT</t>
@@ -2672,13 +2678,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2696,7 +2702,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2713,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2742,10 +2748,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2796,7 +2802,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2813,10 +2819,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2842,10 +2848,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2896,7 +2902,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2913,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2942,10 +2948,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2972,10 +2978,10 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2996,7 +3002,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3013,10 +3019,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3039,13 +3045,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3096,7 +3102,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3108,15 +3114,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3139,13 +3145,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3196,7 +3202,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3213,14 +3219,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3239,16 +3245,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3286,19 +3292,19 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3310,15 +3316,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3341,16 +3347,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3400,7 +3406,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3417,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3443,13 +3449,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3500,7 +3506,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3512,15 +3518,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3546,10 +3552,10 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3600,7 +3606,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3617,10 +3623,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3646,10 +3652,10 @@
         <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3700,7 +3706,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3717,10 +3723,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3746,10 +3752,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3776,10 +3782,10 @@
         <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -3800,7 +3806,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3817,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3843,13 +3849,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3879,7 +3885,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3900,7 +3906,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3976,10 +3982,10 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -4017,10 +4023,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4046,10 +4052,10 @@
         <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4100,7 +4106,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4117,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4143,13 +4149,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4200,7 +4206,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4217,10 +4223,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4246,10 +4252,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4300,7 +4306,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4317,10 +4323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4346,10 +4352,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4376,10 +4382,10 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4400,7 +4406,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4417,10 +4423,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4446,10 +4452,10 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4500,7 +4506,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4517,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4546,10 +4552,10 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4600,7 +4606,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4617,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4643,13 +4649,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4700,7 +4706,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
